--- a/ig/nr-corrections/StructureDefinition-as-dr-person.xlsx
+++ b/ig/nr-corrections/StructureDefinition-as-dr-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:20:08+00:00</t>
+    <t>2024-02-12T14:26:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-corrections/StructureDefinition-as-dr-person.xlsx
+++ b/ig/nr-corrections/StructureDefinition-as-dr-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:26:19+00:00</t>
+    <t>2024-02-12T14:49:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-corrections/StructureDefinition-as-dr-person.xlsx
+++ b/ig/nr-corrections/StructureDefinition-as-dr-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:49:01+00:00</t>
+    <t>2024-02-16T11:05:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
